--- a/output/india/bengaluru/salon/leads.xlsx
+++ b/output/india/bengaluru/salon/leads.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="leads" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -560,6 +560,21 @@
           <t>whatsapp</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>review_status</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>review_notes</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>website_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -587,7 +602,6 @@
           <t>https://missnail.in/index.php/vijaynagar/</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/miss_nail_art._</t>
@@ -598,8 +612,6 @@
           <t>https://www.facebook.com/share/1CPktfsnnR</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/share/1CPktfsnnR, https://www.instagram.com/miss_nail_art._, https://www.instagram.com/missnail.in</t>
@@ -643,6 +655,21 @@
       <c r="S2" t="inlineStr">
         <is>
           <t>YES</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>contains unreplaced template tokens</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>file:///C:/Users/Laptop/OneDrive/Desktop/Creative-client-/output/india/bengaluru/salon/SHOP_E21E66722D/index.html</t>
         </is>
       </c>
     </row>
